--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-31.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,11 @@
           <t>Instrucao_OrbitX</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Str</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -679,6 +684,11 @@
           <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.79` (BFED `6.40` x 1.0616)</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -799,6 +809,11 @@
           <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.58` (BFED `6.20` x 1.0616)</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -919,6 +934,11 @@
           <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.24` (BFED `5.80` x 1.0755)</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1039,6 +1059,11 @@
           <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.58` (BFED `6.20` x 1.0616)</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1157,6 +1182,11 @@
       <c r="Z6" t="inlineStr">
         <is>
           <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.35` (BFED `5.90` x 1.0755)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-31.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,42 +573,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>League 1 (Inglaterra)</t>
+          <t>La Liga (Espanha)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stockport x AFC Wimbledon</t>
+          <t>Levante x Ath Madrid</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ath Madrid</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lay Draw Super Fav (Pré-Registro 31/10)</t>
+          <t>Lay Home Fav Visitante [OBSERVAÇÃO STAKE-ZERO]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The Draw (Empate)</t>
+          <t>Home (Mandante)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -617,25 +617,25 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6.79</v>
+        <v>6.28</v>
       </c>
       <c r="L2" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="M2" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>MATCH_ODDS</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1.0616</v>
+        <v>1.065</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>&lt;= 7.00</t>
+          <t>&lt;= 8.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>+2.87%</t>
+          <t>+6.18%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Football-Data (Exchange BFED)</t>
+          <t>Football-Data (Exchange BFEH)</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.79` (BFED `6.40` x 1.0616)</t>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'Levante' -&gt; Lay Est `6.28` (BFEH `5.90` | Fav Visitante `1.58`)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
     </row>
@@ -708,32 +708,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>National League (Inglaterra)</t>
+          <t>League 1 (Escócia)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Boreham Wood x Hartlepool</t>
+          <t>East Kilbride x Ross County</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>East Kilbride</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lay Draw Super Fav (Pré-Registro 31/10)</t>
+          <t>Lay Home Fav Visitante [OBSERVAÇÃO STAKE-ZERO]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Draw (Empate)</t>
+          <t>Home (Mandante)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -742,25 +742,25 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.58</v>
+        <v>5.01</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>MATCH_ODDS</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1.0616</v>
+        <v>1.065</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>&lt;= 7.00</t>
+          <t>&lt;= 8.00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>+2.87%</t>
+          <t>+6.18%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Football-Data (Exchange BFED)</t>
+          <t>Football-Data (Exchange BFEH)</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.58` (BFED `6.20` x 1.0616)</t>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'East Kilbride' -&gt; Lay Est `5.01` (BFEH `4.70` | Fav Visitante `1.54`)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -823,32 +823,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Super Lig (Turquia)</t>
+          <t>League 1 (Inglaterra)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fenerbahce x Goztep</t>
+          <t>Stockport x AFC Wimbledon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goztep</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -867,21 +867,21 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6.24</v>
+        <v>6.79</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4.5-6.0</t>
+          <t>6.0-8.0</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1.0755</v>
+        <v>1.0616</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,12 +931,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.24` (BFED `5.80` x 1.0755)</t>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.79` (BFED `6.40` x 1.0616)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -948,32 +948,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bundesliga (Alemanha)</t>
+          <t>National League (Inglaterra)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bayern Munich x Dortmund</t>
+          <t>Boreham Wood x Hartlepool</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
     </row>
@@ -1073,32 +1073,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La Liga (Espanha)</t>
+          <t>Super Lig (Turquia)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Betis x Malaga</t>
+          <t>Fenerbahce x Goztep</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Goztep</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.35</v>
+        <v>6.24</v>
       </c>
       <c r="L6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
         <v>1.37</v>
@@ -1181,12 +1181,512 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.24` (BFED `5.80` x 1.0755)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Serie A (Itália)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Udinese x Roma</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lay Home Fav Visitante [OBSERVAÇÃO STAKE-ZERO]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Home (Mandante)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>MATCH_ODDS</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>&lt;= 8.00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>&lt;= 1.15</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>+6.18%</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE (Stake-Zero)</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Football-Data (Exchange BFEH)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'Udinese' -&gt; Lay Est `6.60` (BFEH `6.20` | Fav Visitante `1.58`)</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bundesliga (Alemanha)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bayern Munich x Dortmund</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Lay Draw Super Fav (Pré-Registro 31/10)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>The Draw (Empate)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6.0-8.0</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1.0616</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>&lt;= 7.00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>&lt;= 1.15</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>87.7%</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>+2.87%</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE (Stake-Zero)</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Football-Data (Exchange BFED)</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.58` (BFED `6.20` x 1.0616)</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>La Liga (Espanha)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Betis x Malaga</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lay Draw Super Fav (Pré-Registro 31/10)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The Draw (Empate)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4.5-6.0</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1.0755</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>&lt;= 7.00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>&lt;= 1.15</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>87.7%</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>+2.87%</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE (Stake-Zero)</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Football-Data (Exchange BFED)</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>Acompanhamento Stake-Zero -&gt; Seleção 'The Draw' -&gt; Lay Est `6.35` (BFED `5.90` x 1.0755)</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jupiler Pro League (Bélgica)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Beveren x St. Gilloise</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beveren</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>St. Gilloise</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lay Home Fav Visitante [OBSERVAÇÃO STAKE-ZERO]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Home (Mandante)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>MATCH_ODDS</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>&lt;= 8.00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>&lt;= 1.15</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>+6.18%</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE (Stake-Zero)</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Football-Data (Exchange BFEH)</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Acompanhamento Stake-Zero -&gt; Seleção 'Beveren' -&gt; Lay Est `6.07` (BFEH `5.70` | Fav Visitante `1.46`)</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
     </row>
